--- a/data/trans_orig/Q5413-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5413-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2007</t>
+          <t>Población según si es capaz de vestirse solo en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1856</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32525</t>
+          <t>33457</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66595</t>
+          <t>66548</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73724</t>
+          <t>73716</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,44 +1322,44 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3920</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>9014</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
           <t>9,21%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>3920</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>9676</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60513</t>
+          <t>60522</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82661</t>
+          <t>82357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94055</t>
+          <t>93891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146525</t>
+          <t>146153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159507</t>
+          <t>159264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1758,97 +1758,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1882</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45877</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77806</t>
+          <t>76823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126989</t>
+          <t>127813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2101,97 +2101,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1730</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1799</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50085</t>
+          <t>49565</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68315</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122178</t>
+          <t>122677</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>128614</t>
+          <t>128621</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>845</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>911</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31085</t>
+          <t>31166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40104</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54960</t>
+          <t>56096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66270</t>
+          <t>66338</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -3013,97 +3013,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1926</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3126,97 +3126,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>1926</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45391</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47196</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68329</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115580</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>117506</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,62 +3617,62 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>4181</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98732</t>
+          <t>98643</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105121</t>
+          <t>105115</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108362</t>
+          <t>108100</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116225</t>
+          <t>116221</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>210932</t>
+          <t>211616</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>220879</t>
+          <t>221102</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>100617</t>
+          <t>100127</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>109841</t>
+          <t>109877</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>135129</t>
+          <t>135169</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>147766</t>
+          <t>147653</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>239750</t>
+          <t>239064</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>255892</t>
+          <t>255865</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29237</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>25025</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>41004</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>472201</t>
+          <t>474818</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>489648</t>
+          <t>489784</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>634702</t>
+          <t>634090</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>657079</t>
+          <t>656918</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1116905</t>
+          <t>1115491</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1142557</t>
+          <t>1142066</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2012</t>
+          <t>Población según si es capaz de vestirse solo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,97 +5073,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6554</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2201</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7784</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6924</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2201</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6935</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13997</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>39206</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>31654</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>44451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75252</t>
+          <t>75136</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87603</t>
+          <t>87695</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20179</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23180</t>
+          <t>23647</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29712</t>
+          <t>29255</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64366</t>
+          <t>63677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76111</t>
+          <t>76120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70463</t>
+          <t>69741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87737</t>
+          <t>87853</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140338</t>
+          <t>140916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162184</t>
+          <t>161092</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17317</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11941</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>18144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42075</t>
+          <t>40626</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52686</t>
+          <t>52689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58858</t>
+          <t>59364</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72433</t>
+          <t>73263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>105446</t>
+          <t>105858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122835</t>
+          <t>123119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51251</t>
+          <t>51023</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61733</t>
+          <t>61649</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68900</t>
+          <t>68875</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81264</t>
+          <t>81252</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124179</t>
+          <t>124828</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140049</t>
+          <t>140056</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>969</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12579</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22377</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30490</t>
+          <t>30511</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38397</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47850</t>
+          <t>47889</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65268</t>
+          <t>64870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77264</t>
+          <t>77311</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10552</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43318</t>
+          <t>43187</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50700</t>
+          <t>50701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52108</t>
+          <t>52799</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64761</t>
+          <t>64783</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>98635</t>
+          <t>100438</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114469</t>
+          <t>114444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12833</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>7521</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30389</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>93373</t>
+          <t>92912</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107247</t>
+          <t>107643</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>112835</t>
+          <t>113896</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>129999</t>
+          <t>130349</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>212639</t>
+          <t>212445</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>234407</t>
+          <t>234372</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12426</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11821</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>10519</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>109076</t>
+          <t>108931</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>118686</t>
+          <t>118664</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>136009</t>
+          <t>137553</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>153449</t>
+          <t>153523</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>251058</t>
+          <t>250319</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>270990</t>
+          <t>269898</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26951</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>24979</t>
+          <t>24938</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>50207</t>
+          <t>48761</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>38944</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>69020</t>
+          <t>68963</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>42030</t>
+          <t>42252</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>56097</t>
+          <t>55221</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>88172</t>
+          <t>88580</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>81175</t>
+          <t>81131</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>120438</t>
+          <t>122333</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>498213</t>
+          <t>499982</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>526656</t>
+          <t>527631</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>615047</t>
+          <t>614708</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>654041</t>
+          <t>654242</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1124043</t>
+          <t>1123798</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1172161</t>
+          <t>1172057</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2016</t>
+          <t>Población según si es capaz de vestirse solo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>9749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22927</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>27800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32236</t>
+          <t>33454</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45032</t>
+          <t>45804</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64400</t>
+          <t>64822</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79755</t>
+          <t>79034</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24260</t>
+          <t>24572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76116</t>
+          <t>76021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85415</t>
+          <t>85371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92800</t>
+          <t>92093</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108705</t>
+          <t>108851</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174320</t>
+          <t>173462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192064</t>
+          <t>191970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54784</t>
+          <t>53909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62740</t>
+          <t>62728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67612</t>
+          <t>67305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>78652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126134</t>
+          <t>127947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139890</t>
+          <t>140226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51272</t>
+          <t>52250</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61293</t>
+          <t>61222</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76310</t>
+          <t>75796</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89026</t>
+          <t>88956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>133431</t>
+          <t>133333</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149074</t>
+          <t>148540</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -11237,97 +11237,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2262</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7778</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>15,39%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>2262</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7025</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>7874</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>13,9%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2262</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>7789</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37618</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47411</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78334</t>
+          <t>78218</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89363</t>
+          <t>89433</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19363</t>
+          <t>19443</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38377</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46673</t>
+          <t>46020</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48409</t>
+          <t>48697</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62400</t>
+          <t>62481</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90788</t>
+          <t>91068</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>106351</t>
+          <t>106790</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>18496</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100490</t>
+          <t>100511</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>109547</t>
+          <t>109535</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>127935</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141949</t>
+          <t>141738</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>234353</t>
+          <t>233063</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>250164</t>
+          <t>250185</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -12605,97 +12605,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2364</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18985</t>
+          <t>18752</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>125386</t>
+          <t>126682</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>157312</t>
+          <t>157545</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>171539</t>
+          <t>171556</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>289339</t>
+          <t>289691</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>304315</t>
+          <t>304392</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>33442</t>
+          <t>33367</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>17808</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>40567</t>
+          <t>41615</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38092</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>68878</t>
+          <t>70484</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>62430</t>
+          <t>63388</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>99131</t>
+          <t>100240</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>543110</t>
+          <t>543330</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>565254</t>
+          <t>564893</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>685980</t>
+          <t>683371</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>723587</t>
+          <t>721578</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1239059</t>
+          <t>1240059</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1282359</t>
+          <t>1282610</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2023</t>
+          <t>Población según si es capaz de vestirse solo en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,97 +13753,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51515</t>
+          <t>51273</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>52788</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60298</t>
+          <t>60415</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>107252</t>
+          <t>107391</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115652</t>
+          <t>115956</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13047</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>19324</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22709</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68429</t>
+          <t>68895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78118</t>
+          <t>78037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102048</t>
+          <t>100181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114607</t>
+          <t>114476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174237</t>
+          <t>173712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189642</t>
+          <t>189940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>14605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>25847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56482</t>
+          <t>56562</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66412</t>
+          <t>66085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68864</t>
+          <t>68376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78673</t>
+          <t>78809</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129247</t>
+          <t>129242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142643</t>
+          <t>142159</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71863</t>
+          <t>71395</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89439</t>
+          <t>89173</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96915</t>
+          <t>96852</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>163003</t>
+          <t>162954</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>171113</t>
+          <t>171324</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -15577,97 +15577,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2111</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>423</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>2361</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2147</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>498</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29921</t>
+          <t>30094</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33908</t>
+          <t>34318</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49046</t>
+          <t>49517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55376</t>
+          <t>55309</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81545</t>
+          <t>81580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88533</t>
+          <t>88588</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15015</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51653</t>
+          <t>51605</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57341</t>
+          <t>57447</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49723</t>
+          <t>49381</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57109</t>
+          <t>57006</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>103707</t>
+          <t>103564</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>112778</t>
+          <t>112474</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -16494,7 +16494,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11840</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>578</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26965</t>
+          <t>25912</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>112812</t>
+          <t>113200</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>121105</t>
+          <t>121304</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>305859</t>
+          <t>305625</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>336846</t>
+          <t>336277</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>427208</t>
+          <t>428979</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>457221</t>
+          <t>457589</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -16945,97 +16945,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1196</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2688</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>3262</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>2665</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>17823</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>139506</t>
+          <t>139111</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>145694</t>
+          <t>145282</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>172708</t>
+          <t>171999</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>182010</t>
+          <t>181780</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>314759</t>
+          <t>314751</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>326221</t>
+          <t>326265</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>30414</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>38634</t>
+          <t>39311</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>19970</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>37233</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>37155</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>86347</t>
+          <t>86836</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>63257</t>
+          <t>57681</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>114125</t>
+          <t>113190</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>604537</t>
+          <t>602981</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623462</t>
+          <t>623213</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>919854</t>
+          <t>918959</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>987599</t>
+          <t>984148</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1536595</t>
+          <t>1536618</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1600410</t>
+          <t>1609038</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5413-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5413-Provincia-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29790</t>
+          <t>29651</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33457</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66548</t>
+          <t>66338</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73716</t>
+          <t>73723</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60522</t>
+          <t>60136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82357</t>
+          <t>82412</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93891</t>
+          <t>93954</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146153</t>
+          <t>146212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159264</t>
+          <t>159455</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45309</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76823</t>
+          <t>75863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127813</t>
+          <t>126914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49565</t>
+          <t>50015</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67347</t>
+          <t>69104</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122677</t>
+          <t>121845</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>128621</t>
+          <t>128611</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7613</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>13019</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>30696</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40103</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56096</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66338</t>
+          <t>66401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98643</t>
+          <t>98917</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105115</t>
+          <t>105114</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108100</t>
+          <t>108857</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116221</t>
+          <t>116225</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>211616</t>
+          <t>211419</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>221102</t>
+          <t>221040</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>12634</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>100127</t>
+          <t>99056</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>109877</t>
+          <t>109894</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>135169</t>
+          <t>134619</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>147653</t>
+          <t>148592</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,47 +4201,47 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
+          <t>96,98%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>248804</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>239295</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>255479</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>90,26%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
           <t>96,36%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>248804</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>239064</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>255865</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25025</t>
+          <t>25341</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>41035</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>474818</t>
+          <t>472760</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>489784</t>
+          <t>489621</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>634090</t>
+          <t>634513</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>656918</t>
+          <t>657116</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1115491</t>
+          <t>1117009</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1142066</t>
+          <t>1143491</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13997</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>39365</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31654</t>
+          <t>32586</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44451</t>
+          <t>43415</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75136</t>
+          <t>75525</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87695</t>
+          <t>87756</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>22967</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29255</t>
+          <t>29791</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63677</t>
+          <t>64256</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76120</t>
+          <t>76166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69741</t>
+          <t>70799</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87853</t>
+          <t>88387</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140916</t>
+          <t>140919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161092</t>
+          <t>161766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>14417</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>40642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52689</t>
+          <t>52711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59364</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73263</t>
+          <t>72351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>105858</t>
+          <t>105022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123119</t>
+          <t>122699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,41%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>12505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51023</t>
+          <t>51232</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61649</t>
+          <t>60993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68875</t>
+          <t>68474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81252</t>
+          <t>80427</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124828</t>
+          <t>125172</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140056</t>
+          <t>140185</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22486</t>
+          <t>22366</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47889</t>
+          <t>47852</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64870</t>
+          <t>64693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77311</t>
+          <t>77100</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52799</t>
+          <t>52201</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64783</t>
+          <t>64787</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>100438</t>
+          <t>100655</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114444</t>
+          <t>114458</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22058</t>
+          <t>22867</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12930</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30121</t>
+          <t>31271</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92912</t>
+          <t>93012</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107643</t>
+          <t>107281</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>113896</t>
+          <t>113446</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>130349</t>
+          <t>130327</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>212445</t>
+          <t>212956</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>234372</t>
+          <t>234216</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13178</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>21314</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>10519</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>27609</t>
+          <t>26804</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>108931</t>
+          <t>108419</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>118664</t>
+          <t>118645</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>137553</t>
+          <t>136567</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>153523</t>
+          <t>153369</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>250319</t>
+          <t>251403</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>269898</t>
+          <t>269828</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>24560</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>38577</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>68963</t>
+          <t>68867</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>42855</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>55221</t>
+          <t>54203</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>88580</t>
+          <t>87175</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>81131</t>
+          <t>82527</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>122333</t>
+          <t>122622</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>499982</t>
+          <t>498251</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>527631</t>
+          <t>526582</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>614708</t>
+          <t>617130</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>654242</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1123798</t>
+          <t>1126947</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1172057</t>
+          <t>1173560</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22096</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27800</t>
+          <t>27782</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36353</t>
+          <t>36356</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33454</t>
+          <t>32713</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45804</t>
+          <t>45556</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64822</t>
+          <t>64120</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79034</t>
+          <t>79557</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19168</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24572</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76021</t>
+          <t>75571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85371</t>
+          <t>85033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92093</t>
+          <t>91998</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108851</t>
+          <t>109122</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173462</t>
+          <t>174196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191970</t>
+          <t>191957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53909</t>
+          <t>54928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62728</t>
+          <t>62716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78652</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127947</t>
+          <t>127928</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140226</t>
+          <t>139827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10245</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52250</t>
+          <t>51453</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61222</t>
+          <t>61335</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>75796</t>
+          <t>76174</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88956</t>
+          <t>89059</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>133333</t>
+          <t>133219</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>148540</t>
+          <t>148525</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37755</t>
+          <t>38071</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>48178</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78218</t>
+          <t>79055</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89433</t>
+          <t>89325</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>806</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14971</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19443</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38436</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46020</t>
+          <t>46757</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>48939</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62481</t>
+          <t>62541</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91068</t>
+          <t>90394</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>106790</t>
+          <t>106683</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13663</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>889</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18496</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100511</t>
+          <t>100081</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>109535</t>
+          <t>110243</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>128248</t>
+          <t>128168</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141738</t>
+          <t>142629</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>233063</t>
+          <t>232963</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>250185</t>
+          <t>249985</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>18275</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>20774</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>126682</t>
+          <t>126006</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>157545</t>
+          <t>158022</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>171556</t>
+          <t>172184</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>289691</t>
+          <t>288547</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>304392</t>
+          <t>304378</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>32795</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>41615</t>
+          <t>40932</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>38577</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>38224</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>70484</t>
+          <t>69253</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>63388</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>100240</t>
+          <t>100263</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>543330</t>
+          <t>543780</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>564893</t>
+          <t>565130</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>683371</t>
+          <t>685580</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>721578</t>
+          <t>722336</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1240059</t>
+          <t>1239897</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1282610</t>
+          <t>1281715</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>885</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -13871,12 +13871,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13896,32 +13896,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6059</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13931,32 +13931,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -13974,27 +13974,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55009</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51273</t>
+          <t>56597</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -14009,32 +14009,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57350</t>
+          <t>59424</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52788</t>
+          <t>55567</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>62458</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14044,32 +14044,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112359</t>
+          <t>119494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>107391</t>
+          <t>114718</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115956</t>
+          <t>122811</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -14087,17 +14087,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14204,22 +14204,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14239,32 +14239,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14274,32 +14274,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>18186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -14317,32 +14317,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>921</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14352,32 +14352,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>9315</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14387,32 +14387,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>15990</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22213</t>
+          <t>24886</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -14430,32 +14430,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74538</t>
+          <t>81767</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68895</t>
+          <t>75950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78037</t>
+          <t>85552</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14465,32 +14465,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>108629</t>
+          <t>113527</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>105888</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114476</t>
+          <t>119472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14500,32 +14500,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>183166</t>
+          <t>195294</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173712</t>
+          <t>185788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189940</t>
+          <t>203278</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14578,17 +14578,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14613,17 +14613,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14660,27 +14660,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>551</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -14695,32 +14695,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14730,32 +14730,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -14773,32 +14773,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>14863</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14808,32 +14808,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9803</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14843,32 +14843,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19582</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25847</t>
+          <t>26942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -14886,32 +14886,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>61827</t>
+          <t>60781</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56562</t>
+          <t>55513</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66085</t>
+          <t>64731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14921,32 +14921,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>74283</t>
+          <t>72610</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68376</t>
+          <t>67515</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78809</t>
+          <t>77137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14956,32 +14956,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>136110</t>
+          <t>133391</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129242</t>
+          <t>126125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142159</t>
+          <t>139177</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -14999,17 +14999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15151,32 +15151,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>788</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15186,32 +15186,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>778</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>644</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15264,32 +15264,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15299,32 +15299,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -15342,27 +15342,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73999</t>
+          <t>82512</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71395</t>
+          <t>79887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -15377,32 +15377,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>93555</t>
+          <t>99932</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89173</t>
+          <t>95287</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96852</t>
+          <t>103512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15412,32 +15412,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>167553</t>
+          <t>182443</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>162954</t>
+          <t>178050</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>171324</t>
+          <t>186377</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15490,17 +15490,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15525,17 +15525,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>422</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -15617,12 +15617,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>422</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -15652,12 +15652,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -15685,32 +15685,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>596</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15720,32 +15720,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15755,32 +15755,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -15798,32 +15798,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>32762</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30094</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34318</t>
+          <t>35907</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15833,32 +15833,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52897</t>
+          <t>54857</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49517</t>
+          <t>50942</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55309</t>
+          <t>57505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15868,32 +15868,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>85659</t>
+          <t>89261</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81580</t>
+          <t>84862</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88588</t>
+          <t>92242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -15911,17 +15911,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15946,17 +15946,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15981,17 +15981,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16063,32 +16063,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16098,32 +16098,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -16141,32 +16141,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16176,32 +16176,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,27 +16216,27 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -16254,32 +16254,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>55049</t>
+          <t>54954</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51605</t>
+          <t>51893</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57447</t>
+          <t>57405</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16289,32 +16289,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>53678</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49381</t>
+          <t>51474</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57006</t>
+          <t>59134</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16324,32 +16324,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>108728</t>
+          <t>110507</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>103564</t>
+          <t>105644</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>112474</t>
+          <t>114639</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -16367,17 +16367,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16402,17 +16402,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -16494,12 +16494,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16519,32 +16519,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16554,32 +16554,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -16597,32 +16597,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16632,32 +16632,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>10335</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16667,32 +16667,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25912</t>
+          <t>23999</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -16710,32 +16710,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>118232</t>
+          <t>144999</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>113200</t>
+          <t>137912</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>121304</t>
+          <t>148995</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16745,32 +16745,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>327572</t>
+          <t>150462</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>305625</t>
+          <t>144496</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>336277</t>
+          <t>155961</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16780,32 +16780,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>445804</t>
+          <t>295462</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>428979</t>
+          <t>286378</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>457589</t>
+          <t>302658</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -16823,17 +16823,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16858,17 +16858,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16893,17 +16893,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>592</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -16985,12 +16985,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>592</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -17053,32 +17053,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17088,32 +17088,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17123,32 +17123,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>17823</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -17166,32 +17166,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>143268</t>
+          <t>158850</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>139111</t>
+          <t>154010</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>145282</t>
+          <t>161543</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17201,32 +17201,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>178179</t>
+          <t>202553</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>171999</t>
+          <t>195830</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>181780</t>
+          <t>206855</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17236,32 +17236,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>321447</t>
+          <t>361403</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>314751</t>
+          <t>353148</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>326265</t>
+          <t>366786</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -17279,17 +17279,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17314,17 +17314,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>186169</t>
+          <t>212227</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>186169</t>
+          <t>212227</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>186169</t>
+          <t>212227</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17349,17 +17349,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>333249</t>
+          <t>375781</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>333249</t>
+          <t>375781</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>333249</t>
+          <t>375781</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17396,32 +17396,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17431,32 +17431,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>30414</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17466,32 +17466,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39311</t>
+          <t>38927</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -17509,32 +17509,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>27872</t>
+          <t>30011</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19970</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>40262</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17544,32 +17544,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>65677</t>
+          <t>71194</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>37155</t>
+          <t>60147</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>86836</t>
+          <t>85264</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17579,32 +17579,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>93549</t>
+          <t>101205</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>57681</t>
+          <t>87805</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>113190</t>
+          <t>119424</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -17622,32 +17622,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>614683</t>
+          <t>678336</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>602981</t>
+          <t>667510</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623213</t>
+          <t>687959</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17657,32 +17657,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>946143</t>
+          <t>808918</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>918959</t>
+          <t>794662</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>984148</t>
+          <t>821183</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17692,32 +17692,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1560826</t>
+          <t>1487255</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1536618</t>
+          <t>1469476</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1609038</t>
+          <t>1504675</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -17735,17 +17735,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17770,17 +17770,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1032965</t>
+          <t>902426</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1032965</t>
+          <t>902426</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1032965</t>
+          <t>902426</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17805,17 +17805,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1683143</t>
+          <t>1618818</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1683143</t>
+          <t>1618818</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1683143</t>
+          <t>1618818</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
